--- a/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:23</t>
+          <t>2026-09-02 00:55:07</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:24</t>
+          <t>2026-09-02 00:55:09</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:25</t>
+          <t>2026-09-02 00:55:10</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:27</t>
+          <t>2026-09-02 00:55:11</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:27</t>
+          <t>2026-09-02 00:55:11</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:27</t>
+          <t>2026-09-02 00:55:11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:27</t>
+          <t>2026-09-02 00:55:11</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:27</t>
+          <t>2026-09-02 00:55:11</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-02 00:35:27</t>
+          <t>2026-09-02 00:55:11</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:07</t>
+          <t>2026-09-02 01:21:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:09</t>
+          <t>2026-09-02 01:21:41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:10</t>
+          <t>2026-09-02 01:21:42</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:11</t>
+          <t>2026-09-02 01:21:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:11</t>
+          <t>2026-09-02 01:21:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:11</t>
+          <t>2026-09-02 01:21:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:11</t>
+          <t>2026-09-02 01:21:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:11</t>
+          <t>2026-09-02 01:21:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-02 00:55:11</t>
+          <t>2026-09-02 01:21:43</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">

--- a/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>+1.46%2440</t>
+          <t>-2.25%2385</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>+1.46%</t>
+          <t>-2.25%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2440</v>
+        <v>2385</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>-0.36%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.44%3410</t>
+          <t>-2.93%3310</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-2.93%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>3410</v>
+        <v>3310</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>+9.94%4315</t>
+          <t>-0.93%4275</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-0.93%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>4315</v>
+        <v>4275</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>+2.83%5640</t>
+          <t>-3.46%5445</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>-3.46%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>5640</v>
+        <v>5445</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.15%</t>
+          <t>-0.19%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-2.8%971</t>
+          <t>+0.21%973</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>971</v>
+        <v>973</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+2.71%132.5</t>
+          <t>-4.91%126</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>132.5</v>
+        <v>126</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.75%5885</t>
+          <t>-1.95%5770</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5885</v>
+        <v>5770</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.92%7580</t>
+          <t>+3.03%7810</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.92%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7580</v>
+        <v>7810</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+5.46%5410</t>
+          <t>-2.22%5290</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+5.46%</t>
+          <t>-2.22%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>5410</v>
+        <v>5290</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.19%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+9.94%7800</t>
+          <t>0%2610</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>7800</v>
+        <v>2610</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.30%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>-7.24%1730</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-7.24%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1865</v>
+        <v>1730</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.25%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+8.35%2205</t>
+          <t>-2.95%2140</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+8.35%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2205</v>
+        <v>2140</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.24%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+4.22%568</t>
+          <t>-4.93%540</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+4.22%</t>
+          <t>-4.93%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>568</v>
+        <v>540</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1267,7 +1267,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.14%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-1.72%5995</t>
+          <t>-1.67%5895</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>-1.67%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>5995</v>
+        <v>5895</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:39</t>
+          <t>2026-09-02 16:25:37</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+4.45%610</t>
+          <t>-3.44%589</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-0.41%1225</t>
+          <t>-2.04%1200</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-0.41%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1225</v>
+        <v>1200</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>-6.26%2170</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>-6.26%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2315</v>
+        <v>2170</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+6.72%874</t>
+          <t>-3.09%847</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+6.72%</t>
+          <t>-3.09%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>874</v>
+        <v>847</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.3%234.5</t>
+          <t>+1.28%237.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>234.5</v>
+        <v>237.5</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+8.99%994</t>
+          <t>-2.72%967</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+8.99%</t>
+          <t>-2.72%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>994</v>
+        <v>967</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.14%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+1.05%1450</t>
+          <t>-2.76%1410</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>-2.76%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>1450</v>
+        <v>1410</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+6.57%17120</t>
+          <t>+3.53%17725</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+6.57%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>17120</v>
+        <v>17725</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.87%2285</t>
+          <t>-7.66%2110</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.87%</t>
+          <t>-7.66%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2285</v>
+        <v>2110</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.12%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0%1175</t>
+          <t>+7.66%1265</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+7.66%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1175</v>
+        <v>1265</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.09%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.57%2030</t>
+          <t>-2.71%1975</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>2030</v>
+        <v>1975</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+2.53%284</t>
+          <t>-2.11%278</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+2.53%</t>
+          <t>-2.11%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-3.56%176</t>
+          <t>+1.7%179</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-3.56%</t>
+          <t>+1.7%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+5.05%406</t>
+          <t>-3.45%392</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+5.05%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>406</v>
+        <v>392</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+2.4%256</t>
+          <t>-1.95%251</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+2.4%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:41</t>
+          <t>2026-09-02 16:25:38</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+0.17%5870</t>
+          <t>-2.73%5710</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-2.73%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>5870</v>
+        <v>5710</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+6.77%773</t>
+          <t>-2.07%757</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+6.77%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>773</v>
+        <v>757</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.25%625</t>
+          <t>-3.68%602</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.25%</t>
+          <t>-3.68%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>625</v>
+        <v>602</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-0.21%14150</t>
+          <t>-2.01%13865</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>-2.01%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>14150</v>
+        <v>13865</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+8.56%279</t>
+          <t>-3.05%270.5</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+8.56%</t>
+          <t>-3.05%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>279</v>
+        <v>270.5</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,16 +2583,16 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>+3.25%1745</t>
+          <t>-2.29%1705</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+3.25%</t>
+          <t>-2.29%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>1745</v>
+        <v>1705</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>+0.31%1635</t>
+          <t>+9.79%1795</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+9.79%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>1635</v>
+        <v>1795</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,16 +2705,16 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-2.78%122.5</t>
+          <t>+0.41%123</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-2.78%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>122.5</v>
+        <v>123</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-2.59%526</t>
+          <t>-4.37%503</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+3.77%1100</t>
+          <t>-6.82%1025</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+3.77%</t>
+          <t>-6.82%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1100</v>
+        <v>1025</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>+2.67%84.7</t>
+          <t>-4.6%80.8</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>+2.67%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>84.7</v>
+        <v>80.8</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+8.93%744</t>
+          <t>-5.38%704</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+8.93%</t>
+          <t>-5.38%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>744</v>
+        <v>704</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>+9.85%524</t>
+          <t>+3.44%542</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+9.85%</t>
+          <t>+3.44%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>524</v>
+        <v>542</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+4.17%237.5</t>
+          <t>-1.68%233.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+4.17%</t>
+          <t>-1.68%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>237.5</v>
+        <v>233.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+0.35%580</t>
+          <t>-0.17%579</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+0.35%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:42</t>
+          <t>2026-09-02 16:25:39</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+2.05%249</t>
+          <t>-1.41%245.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+2.05%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>249</v>
+        <v>245.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:43</t>
+          <t>2026-09-02 16:25:41</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-1.85%2125</t>
+          <t>-2.82%2065</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-1.85%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2125</v>
+        <v>2065</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:43</t>
+          <t>2026-09-02 16:25:41</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>+4.54%507</t>
+          <t>-2.96%492</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+4.54%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>507</v>
+        <v>492</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:43</t>
+          <t>2026-09-02 16:25:41</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>+7%535</t>
+          <t>-5.23%507</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>-5.23%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>535</v>
+        <v>507</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:43</t>
+          <t>2026-09-02 16:25:41</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+2.57%359</t>
+          <t>-1.95%352</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+2.57%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:43</t>
+          <t>2026-09-02 16:25:41</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.32%153.5</t>
+          <t>-2.61%149.5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.32%</t>
+          <t>-2.61%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>153.5</v>
+        <v>149.5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-02 01:21:43</t>
+          <t>2026-09-02 16:25:41</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+3.97%157</t>
+          <t>-5.73%148</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+3.97%</t>
+          <t>-5.73%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>157</v>
+        <v>148</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M52"/>
+  <dimension ref="A1:M53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,20 +522,20 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15.86%10,800,000</t>
+          <t>15.59%10,500,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>15.86%</t>
+          <t>15.59%</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>10800000</v>
+        <v>10500000</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.36%</t>
+          <t>-0.35%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.47%3,150,000</t>
+          <t>6.49%3,150,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.47%</t>
+          <t>6.49%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.48%2,110,000</t>
+          <t>5.62%2,110,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.48%</t>
+          <t>5.62%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4.95%8,460,000</t>
+          <t>5.13%8,460,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.95%</t>
+          <t>5.13%</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>3653健策</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-4.91%126</t>
+          <t>-1.95%5770</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-4.91%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>126</v>
+        <v>5770</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3.99%50,000,000</t>
+          <t>4.01%1,115,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>3.99%</t>
+          <t>4.01%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>50000000</v>
+        <v>1115000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>-0.20%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -870,38 +870,38 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3653健策</t>
+          <t>3008大立光</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-1.95%5770</t>
+          <t>+3.03%7810</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>+3.03%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>5770</v>
+        <v>7810</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.95%1,115,000</t>
+          <t>3.94%810,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.95%</t>
+          <t>3.94%</t>
         </is>
       </c>
       <c r="K8" t="n">
-        <v>1115000</v>
+        <v>810000</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3008大立光</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>+3.03%7810</t>
+          <t>-4.91%126</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>+3.03%</t>
+          <t>-4.91%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>7810</v>
+        <v>126</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.70%810,000</t>
+          <t>3.92%50,000,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.70%</t>
+          <t>3.92%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>810000</v>
+        <v>50000000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>+0.11%</t>
+          <t>-0.20%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1010,12 +1010,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.58%1,100,000</t>
+          <t>3.62%1,100,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.58%</t>
+          <t>3.62%</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,16 +1071,16 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.29%700,000</t>
+          <t>3.39%2,087,956</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.39%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>700000</v>
+        <v>2087956</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-7.24%1730</t>
+          <t>-2.95%2140</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-7.24%</t>
+          <t>-2.95%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>1730</v>
+        <v>2140</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.23%2,880,000</t>
+          <t>3.07%2,307,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.23%</t>
+          <t>3.07%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>2880000</v>
+        <v>2307000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>-0.25%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1175,38 +1175,38 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-2.95%2140</t>
+          <t>-7.24%1730</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-2.95%</t>
+          <t>-7.24%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>2140</v>
+        <v>1730</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.06%2,307,000</t>
+          <t>2.96%2,750,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>2.96%</t>
         </is>
       </c>
       <c r="K13" t="n">
-        <v>2307000</v>
+        <v>2750000</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.23%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.74%8,000,000</t>
+          <t>2.69%8,000,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.74%</t>
+          <t>2.69%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.35%650,000</t>
+          <t>2.39%650,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.35%</t>
+          <t>2.39%</t>
         </is>
       </c>
       <c r="K15" t="n">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:37</t>
+          <t>2026-09-02 19:48:57</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-3.44%589</t>
+          <t>+3.53%17725</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>+3.53%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>589</v>
+        <v>17725</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.20%6,000,000</t>
+          <t>2.09%189,500</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.09%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>6000000</v>
+        <v>189500</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>8046南電</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-2.04%1200</t>
+          <t>+1.28%237.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-2.04%</t>
+          <t>+1.28%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1200</v>
+        <v>237.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.95%2,640,000</t>
+          <t>2.00%13,500,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.95%</t>
+          <t>2.00%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>2640000</v>
+        <v>13500000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>8046南電</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-6.26%2170</t>
+          <t>-2.04%1200</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-6.26%</t>
+          <t>-2.04%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>2170</v>
+        <v>1200</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.80%1,293,000</t>
+          <t>1.97%2,640,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.80%</t>
+          <t>1.97%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1293000</v>
+        <v>2640000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>+1.28%237.5</t>
+          <t>-6.26%2170</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>+1.28%</t>
+          <t>-6.26%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>237.5</v>
+        <v>2170</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.69%12,000,000</t>
+          <t>1.75%1,293,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.75%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>12000000</v>
+        <v>1293000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.11%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.68%2,800,000</t>
+          <t>1.69%2,800,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.68%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.66%1,900,000</t>
+          <t>1.67%1,900,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.66%</t>
+          <t>1.67%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+3.53%17725</t>
+          <t>-3.44%589</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+3.53%</t>
+          <t>-3.44%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>17725</v>
+        <v>589</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.54%149,500</t>
+          <t>1.65%4,500,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.65%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>149500</v>
+        <v>4500000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.06%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6805富世達</t>
+          <t>8996高力</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-7.66%2110</t>
+          <t>+7.66%1265</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-7.66%</t>
+          <t>+7.66%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>2110</v>
+        <v>1265</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.44%1,050,000</t>
+          <t>1.37%1,737,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.44%</t>
+          <t>1.37%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>1050000</v>
+        <v>1737000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.12%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,25 +1907,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>8996高力</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+7.66%1265</t>
+          <t>-2.71%1975</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+7.66%</t>
+          <t>-2.71%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>1265</v>
+        <v>1975</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.23%1,737,000</t>
+          <t>1.23%1,000,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -1934,11 +1934,11 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>1737000</v>
+        <v>1000000</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>6805富世達</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-2.71%1975</t>
+          <t>-7.66%2110</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-2.71%</t>
+          <t>-7.66%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>1975</v>
+        <v>2110</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.22%1,000,000</t>
+          <t>1.12%850,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.12%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1000000</v>
+        <v>850000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.92%5,360,000</t>
+          <t>0.93%5,360,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.93%</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,16 +2108,16 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>0.74%7,000,000</t>
+          <t>0.56%5,000,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>0.74%</t>
+          <t>0.56%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>7000000</v>
+        <v>5000000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3211順達</t>
+          <t>2317鴻海</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-3.45%392</t>
+          <t>-1.95%251</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-3.45%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>392</v>
+        <v>251</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>0.49%2,000,000</t>
+          <t>0.50%3,200,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>2000000</v>
+        <v>3200000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2317鴻海</t>
+          <t>3211順達</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-1.95%251</t>
+          <t>-3.45%392</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-3.45%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>251</v>
+        <v>392</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.49%3,200,000</t>
+          <t>0.49%2,000,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>3200000</v>
+        <v>2000000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:38</t>
+          <t>2026-09-02 19:48:58</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3583辛耘</t>
+          <t>3450聯鈞</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-2.07%757</t>
+          <t>-3.68%602</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-2.07%</t>
+          <t>-3.68%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>757</v>
+        <v>602</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.37%800,000</t>
+          <t>0.41%1,100,000</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.41%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>800000</v>
+        <v>1100000</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,34 +2395,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>3450聯鈞</t>
+          <t>3583辛耘</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.68%602</t>
+          <t>-2.07%757</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.68%</t>
+          <t>-2.07%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>602</v>
+        <v>757</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.32%860,000</t>
+          <t>0.38%800,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.38%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>860000</v>
+        <v>800000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.26%250,000</t>
+          <t>0.27%250,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.26%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.22%225,000</t>
+          <t>0.25%225,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.25%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2700,38 +2700,38 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2337旺宏</t>
+          <t>1717長興</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>+0.41%123</t>
+          <t>-4.6%80.8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>+0.41%</t>
+          <t>-4.6%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>123</v>
+        <v>80.8</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.22%3,000,000</t>
+          <t>0.16%3,100,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.22%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K38" t="n">
-        <v>3000000</v>
+        <v>3100000</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>2404漢唐</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-4.37%503</t>
+          <t>-6.82%1025</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-4.37%</t>
+          <t>-6.82%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>503</v>
+        <v>1025</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.19%600,000</t>
+          <t>0.16%250,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.19%</t>
+          <t>0.16%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>600000</v>
+        <v>250000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2404漢唐</t>
+          <t>2337旺宏</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-6.82%1025</t>
+          <t>+0.41%123</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-6.82%</t>
+          <t>+0.41%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>1025</v>
+        <v>123</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.17%250,000</t>
+          <t>0.15%2,000,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.17%</t>
+          <t>0.15%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>250000</v>
+        <v>2000000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2883,34 +2883,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1717長興</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-4.6%80.8</t>
+          <t>-4.37%503</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-4.6%</t>
+          <t>-4.37%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>80.8</v>
+        <v>503</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.16%3,100,000</t>
+          <t>0.13%400,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.16%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K41" t="n">
-        <v>3100000</v>
+        <v>400000</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.12%386,000</t>
+          <t>0.13%386,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.13%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,25 +3127,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4966譜瑞-KY</t>
+          <t>2882國泰金</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-0.17%579</t>
+          <t>-1.8%109</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-0.17%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>579</v>
+        <v>109</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.08%220,000</t>
+          <t>0.08%1,200,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3154,7 +3154,7 @@
         </is>
       </c>
       <c r="K45" t="n">
-        <v>220000</v>
+        <v>1200000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:39</t>
+          <t>2026-09-02 19:48:59</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,34 +3188,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6285啟碁</t>
+          <t>4966譜瑞-KY</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-1.41%245.5</t>
+          <t>-0.17%579</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-1.41%</t>
+          <t>-0.17%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>245.5</v>
+        <v>579</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.05%350,000</t>
+          <t>0.08%220,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.05%</t>
+          <t>0.08%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>350000</v>
+        <v>220000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:41</t>
+          <t>2026-09-02 19:49:01</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3249,34 +3249,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>8299群聯</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>-2.82%2065</t>
+          <t>+4.83%315</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>-2.82%</t>
+          <t>+4.83%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>2065</v>
+        <v>315</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.06%300,000</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.06%</t>
         </is>
       </c>
       <c r="K47" t="n">
-        <v>1000</v>
+        <v>300000</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:41</t>
+          <t>2026-09-02 19:49:01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3310,38 +3310,38 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>6285啟碁</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.96%492</t>
+          <t>-1.41%245.5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.96%</t>
+          <t>-1.41%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>492</v>
+        <v>245.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0%1,000</t>
+          <t>0.05%350,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0.05%</t>
         </is>
       </c>
       <c r="K48" t="n">
-        <v>1000</v>
+        <v>350000</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:41</t>
+          <t>2026-09-02 19:49:01</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3371,21 +3371,21 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>8299群聯</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-5.23%507</t>
+          <t>-2.82%2065</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-5.23%</t>
+          <t>-2.82%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>507</v>
+        <v>2065</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:41</t>
+          <t>2026-09-02 19:49:01</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,21 +3432,21 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>2049上銀</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-1.95%352</t>
+          <t>-2.96%492</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-1.95%</t>
+          <t>-2.96%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>352</v>
+        <v>492</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:41</t>
+          <t>2026-09-02 19:49:01</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,21 +3493,21 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>5347世界</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-2.61%149.5</t>
+          <t>-5.23%507</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-2.61%</t>
+          <t>-5.23%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>149.5</v>
+        <v>507</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-02 16:25:41</t>
+          <t>2026-09-02 19:49:01</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3554,21 +3554,21 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>2481強茂</t>
+          <t>2049上銀</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-5.73%148</t>
+          <t>-1.95%352</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-5.73%</t>
+          <t>-1.95%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>148</v>
+        <v>352</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3589,6 +3589,67 @@
         </is>
       </c>
       <c r="M52" t="inlineStr">
+        <is>
+          <t>登入查看</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>00403A</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>2026-09-02 19:49:01</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>https://www.etfinfo.tw/etf/00403A/holdings</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>4</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2481強茂</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-5.73%148</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>-5.73%</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>148</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>0%1,000</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="K53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>+0.00%</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
         <is>
           <t>登入查看</t>
         </is>

--- a/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:57</t>
+          <t>2026-09-02 22:20:54</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:58</t>
+          <t>2026-09-02 22:20:55</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 19:48:59</t>
+          <t>2026-09-02 22:20:57</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:01</t>
+          <t>2026-09-02 22:20:58</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:01</t>
+          <t>2026-09-02 22:20:58</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:01</t>
+          <t>2026-09-02 22:20:58</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:01</t>
+          <t>2026-09-02 22:20:58</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:01</t>
+          <t>2026-09-02 22:20:58</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:01</t>
+          <t>2026-09-02 22:20:58</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-02 19:49:01</t>
+          <t>2026-09-02 22:20:58</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">

--- a/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-02_00403A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:54</t>
+          <t>2026-09-02 23:17:02</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:55</t>
+          <t>2026-09-02 23:17:03</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:57</t>
+          <t>2026-09-02 23:17:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:58</t>
+          <t>2026-09-02 23:17:06</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:58</t>
+          <t>2026-09-02 23:17:06</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:58</t>
+          <t>2026-09-02 23:17:06</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:58</t>
+          <t>2026-09-02 23:17:06</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:58</t>
+          <t>2026-09-02 23:17:06</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:58</t>
+          <t>2026-09-02 23:17:06</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-02 22:20:58</t>
+          <t>2026-09-02 23:17:06</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
